--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="295">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -148,18 +148,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字;
-updator: 更新操作
-sort: 排序字段名
-selector: 查询结果列
-skip：跳过多少行
-returnnum：最大返回条数
-filter：查询条件
-returnnew:是否返回更新后记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>queryandremove</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1120,30 +1108,6 @@
   </si>
   <si>
     <t>枚举集合中的大对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cmd：命令字; 
-name：cl名字; 
-source: 源数据组;
-target: 目标数据组;
-splitpercent: 百分比
-splitquery: 条件
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isasync：是否异常</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1321,6 +1285,54 @@
   </si>
   <si>
     <t>name：组名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+sort: 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum：最大返回条数
+filter：查询条件
+hint:指定索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字;
+updator: 更新操作
+sort: 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum：最大返回条数
+filter：查询条件
+returnnew:是否返回更新后记录
+hint:指定索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cmd：命令字; 
+name：cl名字; 
+source: 源数据组;
+target: 目标数据组;
+splitpercent: 百分比
+splitquery: 条件
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isasync：是否异步</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1500,12 +1512,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1541,6 +1547,12 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1912,12 +1924,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1948,1954 +1960,1954 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="11"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="36">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="96">
+      <c r="A3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="84">
-      <c r="A3" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="G3" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="120">
+      <c r="A4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="84">
+      <c r="A5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="108">
-      <c r="A4" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="15" t="s">
+      <c r="F5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="84">
-      <c r="A5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="36">
+      <c r="A6" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="B6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="36">
-      <c r="A6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="18" t="s">
+      <c r="G6" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="48">
+      <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="B7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="48">
-      <c r="A7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="18" t="s">
+      <c r="G7" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60">
+      <c r="A8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="B8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60">
-      <c r="A8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="18" t="s">
+      <c r="G8" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="24">
+      <c r="A9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="B9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="24">
-      <c r="A9" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="G9" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36">
+      <c r="A10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="B10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="36">
-      <c r="A10" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="18" t="s">
+      <c r="G10" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="84">
+      <c r="A11" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="B11" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="84">
-      <c r="A11" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>105</v>
+      <c r="G11" s="24" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24">
       <c r="A13" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="60">
       <c r="A15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="12" customFormat="1">
+      <c r="A20" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="14" customFormat="1">
-      <c r="A20" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>254</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>255</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" s="14" customFormat="1">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:7" s="12" customFormat="1">
+      <c r="A21" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
+      <c r="A25" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36">
+      <c r="A27" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="24">
+      <c r="A28" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="48">
+      <c r="A29" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="24">
+      <c r="A30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="48">
+      <c r="A32" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="48">
+      <c r="A33" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="72">
+      <c r="A34" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="72">
+      <c r="A35" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="48">
+      <c r="A36" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="48">
+      <c r="A37" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" spans="1:7" ht="60">
+      <c r="A38" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="F38" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" spans="1:7" ht="60">
+      <c r="A39" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" spans="1:7" ht="48">
+      <c r="A40" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" spans="1:7" ht="48">
+      <c r="A41" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="48">
+      <c r="A42" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="24">
+      <c r="A43" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" spans="1:7" ht="48">
+      <c r="A44" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="45" spans="1:7" ht="48">
+      <c r="A45" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" spans="1:7" ht="48">
+      <c r="A46" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" spans="1:7" ht="48">
+      <c r="A47" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" spans="1:7" ht="48">
+      <c r="A48" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G48" s="13"/>
+    </row>
+    <row r="49" spans="1:7" ht="48">
+      <c r="A49" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G49" s="13"/>
+    </row>
+    <row r="50" spans="1:7" ht="48">
+      <c r="A50" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="13"/>
+    </row>
+    <row r="51" spans="1:7" ht="48">
+      <c r="A51" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G51" s="13"/>
+    </row>
+    <row r="52" spans="1:7" ht="48">
+      <c r="A52" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" s="13"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" spans="1:7" ht="24">
+      <c r="A54" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="36">
-      <c r="A27" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="24">
-      <c r="A28" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="48">
-      <c r="A29" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="24">
-      <c r="A30" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="48">
-      <c r="A32" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="48">
-      <c r="A33" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="72">
-      <c r="A34" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="72">
-      <c r="A35" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="48">
-      <c r="A36" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="48">
-      <c r="A37" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="15"/>
-    </row>
-    <row r="38" spans="1:7" ht="60">
-      <c r="A38" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G38" s="26"/>
-    </row>
-    <row r="39" spans="1:7" ht="60">
-      <c r="A39" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="G39" s="26"/>
-    </row>
-    <row r="40" spans="1:7" ht="48">
-      <c r="A40" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="1:7" ht="48">
-      <c r="A41" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="48">
-      <c r="A42" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G42" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="24">
-      <c r="A43" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="15"/>
-    </row>
-    <row r="44" spans="1:7" ht="48">
-      <c r="A44" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="1:7" ht="48">
-      <c r="A45" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G45" s="15"/>
-    </row>
-    <row r="46" spans="1:7" ht="48">
-      <c r="A46" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="G46" s="15"/>
-    </row>
-    <row r="47" spans="1:7" ht="48">
-      <c r="A47" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="15"/>
-    </row>
-    <row r="48" spans="1:7" ht="48">
-      <c r="A48" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="G48" s="15"/>
-    </row>
-    <row r="49" spans="1:7" ht="48">
-      <c r="A49" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" s="15"/>
-    </row>
-    <row r="50" spans="1:7" ht="48">
-      <c r="A50" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" s="15"/>
-    </row>
-    <row r="51" spans="1:7" ht="48">
-      <c r="A51" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G51" s="15"/>
-    </row>
-    <row r="52" spans="1:7" ht="48">
-      <c r="A52" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G52" s="15"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-    </row>
-    <row r="54" spans="1:7" ht="24">
-      <c r="A54" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56" spans="1:7" ht="60">
       <c r="A56" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>188</v>
-      </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
+      <c r="A57" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="20"/>
+      <c r="C57" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
     </row>
     <row r="58" spans="1:7" ht="48">
       <c r="A58" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>88</v>
+        <v>188</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>88</v>
+        <v>189</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E60" s="3" t="s">
+    </row>
+    <row r="61" spans="1:7" ht="24">
+      <c r="A61" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="24">
-      <c r="A61" s="12" t="s">
+      <c r="B61" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="C61" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E62" s="3" t="s">
+    </row>
+    <row r="63" spans="1:7" ht="24">
+      <c r="A63" s="10" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="24">
-      <c r="A63" s="12" t="s">
+      <c r="B63" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B63" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
+      <c r="C63" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" spans="1:7" ht="24">
       <c r="A64" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="24">
       <c r="A65" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B66" s="22"/>
-      <c r="C66" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="B68" s="20"/>
+      <c r="C68" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="20"/>
+      <c r="C69" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="20"/>
+      <c r="C70" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" s="20"/>
+      <c r="C71" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="20"/>
+      <c r="C72" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="20"/>
+      <c r="C73" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="20"/>
+      <c r="C74" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B69" s="22"/>
-      <c r="C69" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B71" s="22"/>
-      <c r="C71" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B74" s="22"/>
-      <c r="C74" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="12" t="s">
+      <c r="C75" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E75" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B75" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:7" ht="36">
       <c r="A76" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>88</v>
+        <v>210</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="24">
       <c r="A78" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>88</v>
+        <v>218</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>88</v>
+        <v>221</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C83" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="22"/>
-      <c r="C84" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="21" t="s">
+      <c r="B86" s="20"/>
+      <c r="C86" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="19"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B86" s="22"/>
-      <c r="C86" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D86" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="21" t="s">
+      <c r="B87" s="20"/>
+      <c r="C87" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E87" s="19"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="19"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B87" s="22"/>
-      <c r="C87" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D87" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="21" t="s">
+      <c r="B88" s="20"/>
+      <c r="C88" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" s="19"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B88" s="22"/>
-      <c r="C88" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E88" s="21"/>
-      <c r="F88" s="21"/>
-      <c r="G88" s="21"/>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="21" t="s">
+      <c r="B89" s="20"/>
+      <c r="C89" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="22"/>
-      <c r="C89" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D89" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E89" s="21"/>
-      <c r="F89" s="21"/>
-      <c r="G89" s="21"/>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="21" t="s">
+      <c r="B90" s="20"/>
+      <c r="C90" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E90" s="19"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B90" s="22"/>
-      <c r="C90" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D90" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="21"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="21" t="s">
+      <c r="B91" s="20"/>
+      <c r="C91" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="22"/>
-      <c r="C91" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D91" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21"/>
-      <c r="G91" s="21"/>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="21" t="s">
+      <c r="B92" s="20"/>
+      <c r="C92" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="19"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B92" s="22"/>
-      <c r="C92" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D92" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B93" s="22"/>
-      <c r="C93" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-      <c r="G93" s="21"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="19"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="19"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D94" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="21" t="s">
+      <c r="B96" s="20"/>
+      <c r="C96" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B95" s="22"/>
-      <c r="C95" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D95" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E95" s="21"/>
-      <c r="F95" s="21"/>
-      <c r="G95" s="21"/>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E96" s="21"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="21"/>
+      <c r="D96" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="19"/>
     </row>
     <row r="97" spans="1:7" ht="48">
       <c r="A97" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="60">
       <c r="A98" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="48">
       <c r="A99" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="C100" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="21" t="s">
+      <c r="G100" s="19"/>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D101" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19"/>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="B100" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="D100" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21" t="s">
+      <c r="B102" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="G100" s="21"/>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="21" t="s">
+      <c r="C102" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E102" s="19"/>
+      <c r="F102" s="19"/>
+      <c r="G102" s="19"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="B103" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="C101" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="D101" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="21" t="s">
+      <c r="C103" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B102" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="D102" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="C103" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
+      <c r="D103" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
+      <c r="G103" s="19"/>
     </row>
     <row r="104" spans="1:7" ht="24">
       <c r="A104" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="48">
       <c r="A105" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="1:7">

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="301">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1333,6 +1333,31 @@
       </rPr>
       <t>isasync：是否异步</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>alter domain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改domain属性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain：域名
+options：选项</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2713,7 +2738,7 @@
         <v>55</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>101</v>
+        <v>296</v>
       </c>
       <c r="D38" s="25" t="s">
         <v>143</v>
@@ -2734,7 +2759,7 @@
         <v>57</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>101</v>
+        <v>296</v>
       </c>
       <c r="D39" s="25" t="s">
         <v>143</v>
@@ -3910,12 +3935,22 @@
         <v>291</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="3"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="3"/>
+    <row r="107" spans="1:7" ht="24">
+      <c r="A107" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="3"/>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">operations!$A$1:$I$108</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -641,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="321">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2092,6 +2091,10 @@
       </rPr>
       <t>SdbUser/SdbPasswd/SdbSessionAtrr</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前处理、后处理</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2354,14 +2357,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2725,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
@@ -2737,8 +2740,13 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="27">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2784,10 +2792,10 @@
       <c r="G1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="39"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" ht="36">
       <c r="A2" s="13" t="s">
@@ -3093,7 +3101,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="24">
+    <row r="14" spans="1:9">
       <c r="A14" s="32" t="s">
         <v>215</v>
       </c>
@@ -3194,7 +3202,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="24">
+    <row r="19" spans="1:9">
       <c r="A19" s="32" t="s">
         <v>297</v>
       </c>
@@ -3205,7 +3213,7 @@
       <c r="F19" s="9"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:9" ht="24">
+    <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
         <v>221</v>
       </c>
@@ -3457,7 +3465,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="36">
+    <row r="32" spans="1:9" ht="24">
       <c r="A32" s="28" t="s">
         <v>306</v>
       </c>
@@ -4061,7 +4069,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="24">
+    <row r="58" spans="1:9">
       <c r="A58" s="19" t="s">
         <v>136</v>
       </c>
@@ -4116,7 +4124,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="24">
+    <row r="61" spans="1:9">
       <c r="A61" s="3" t="s">
         <v>147</v>
       </c>
@@ -4156,7 +4164,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:9" ht="24">
+    <row r="63" spans="1:9">
       <c r="A63" s="3" t="s">
         <v>148</v>
       </c>
@@ -4255,7 +4263,7 @@
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
     </row>
-    <row r="68" spans="1:9" ht="24">
+    <row r="68" spans="1:9">
       <c r="A68" s="3" t="s">
         <v>149</v>
       </c>
@@ -4297,7 +4305,7 @@
       <c r="H69" s="10"/>
       <c r="I69" s="19"/>
     </row>
-    <row r="70" spans="1:9" ht="24">
+    <row r="70" spans="1:9">
       <c r="A70" s="19" t="s">
         <v>151</v>
       </c>
@@ -4318,7 +4326,7 @@
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
     </row>
-    <row r="71" spans="1:9" ht="24">
+    <row r="71" spans="1:9">
       <c r="A71" s="19" t="s">
         <v>140</v>
       </c>
@@ -4443,7 +4451,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="24">
+    <row r="78" spans="1:9">
       <c r="A78" s="3" t="s">
         <v>153</v>
       </c>
@@ -4481,7 +4489,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="36">
+    <row r="80" spans="1:9" ht="24">
       <c r="A80" s="3" t="s">
         <v>155</v>
       </c>
@@ -4500,7 +4508,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="36">
+    <row r="81" spans="1:9" ht="24">
       <c r="A81" s="3" t="s">
         <v>156</v>
       </c>
@@ -4538,7 +4546,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="24">
+    <row r="83" spans="1:9">
       <c r="A83" s="3" t="s">
         <v>158</v>
       </c>
@@ -4593,7 +4601,7 @@
       <c r="H85" s="19"/>
       <c r="I85" s="19"/>
     </row>
-    <row r="86" spans="1:9" ht="24">
+    <row r="86" spans="1:9">
       <c r="A86" s="3" t="s">
         <v>161</v>
       </c>
@@ -4646,7 +4654,7 @@
       <c r="H88" s="19"/>
       <c r="I88" s="19"/>
     </row>
-    <row r="89" spans="1:9" ht="24">
+    <row r="89" spans="1:9">
       <c r="A89" s="19" t="s">
         <v>164</v>
       </c>
@@ -4663,7 +4671,7 @@
       <c r="H89" s="19"/>
       <c r="I89" s="19"/>
     </row>
-    <row r="90" spans="1:9" ht="24">
+    <row r="90" spans="1:9">
       <c r="A90" s="19" t="s">
         <v>165</v>
       </c>
@@ -4680,7 +4688,7 @@
       <c r="H90" s="19"/>
       <c r="I90" s="19"/>
     </row>
-    <row r="91" spans="1:9" ht="24">
+    <row r="91" spans="1:9">
       <c r="A91" s="19" t="s">
         <v>166</v>
       </c>
@@ -4697,7 +4705,7 @@
       <c r="H91" s="19"/>
       <c r="I91" s="19"/>
     </row>
-    <row r="92" spans="1:9" ht="24">
+    <row r="92" spans="1:9">
       <c r="A92" s="19" t="s">
         <v>167</v>
       </c>
@@ -4714,7 +4722,7 @@
       <c r="H92" s="19"/>
       <c r="I92" s="19"/>
     </row>
-    <row r="93" spans="1:9" ht="24">
+    <row r="93" spans="1:9">
       <c r="A93" s="19" t="s">
         <v>168</v>
       </c>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="2" r:id="rId1"/>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="322">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2095,6 +2095,10 @@
   </si>
   <si>
     <t>前处理、后处理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3304,7 +3308,7 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>301</v>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -142,47 +142,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>orderby
-returnnum-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>limit
-filter-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">matcher
+          <t xml:space="preserve">orderby
 </t>
         </r>
         <r>
@@ -271,84 +231,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-deletor= </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>mather</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-增加</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>matcher hint</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="G11" authorId="0">
       <text>
         <r>
@@ -369,46 +251,6 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-splitquery-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>lowbound
-splitendquery  -</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>upbound
 isasync</t>
         </r>
         <r>
@@ -440,84 +282,6 @@
           </rPr>
           <t xml:space="preserve">里
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-options-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>》</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> lowbound+upbound</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-表名统一</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>collectionname</t>
         </r>
       </text>
     </comment>
@@ -682,11 +446,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">cmd：命令字; 
-name：cl名字; </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>insert</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1582,11 +1341,6 @@
   </si>
   <si>
     <t>从主分区集合中分离出子分区集合</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>subclname：子分区集合全名
-options：分区范围</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2099,6 +1853,21 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+matcher:条件;
+hint:指定索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd:命令字
+collectionname：主表名字；
+subclname：子分区集合全名
+lowbound：开始范围
+upbound：结束范围</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2740,17 +2509,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="27">
       <c r="A2" s="38" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -2782,16 +2551,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>2</v>
@@ -2803,364 +2572,364 @@
     </row>
     <row r="2" spans="1:9" ht="36">
       <c r="A2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="C2" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="96">
       <c r="A3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H3" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>101</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="120">
       <c r="A4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="84">
       <c r="A5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36">
       <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48">
       <c r="A7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60">
       <c r="A8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="24">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="48">
       <c r="A9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="36">
       <c r="A10" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>29</v>
-      </c>
       <c r="C10" s="29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="84">
       <c r="A11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="60">
+      <c r="A13" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="48">
-      <c r="A13" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>234</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="34" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
     </row>
     <row r="15" spans="1:9" ht="60">
       <c r="A15" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="24">
       <c r="A16" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>218</v>
-      </c>
       <c r="C16" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="19"/>
@@ -3168,47 +2937,47 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="48">
       <c r="A18" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="32" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -3219,77 +2988,77 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="12" customFormat="1" ht="36">
       <c r="A21" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" s="12" customFormat="1" ht="36">
       <c r="A22" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="19"/>
@@ -3297,54 +3066,54 @@
     </row>
     <row r="24" spans="1:9" ht="36">
       <c r="A24" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="19"/>
@@ -3352,21 +3121,21 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="36">
@@ -3377,21 +3146,21 @@
         <v>7</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="24">
@@ -3402,46 +3171,46 @@
         <v>9</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="48">
       <c r="A30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>90</v>
-      </c>
       <c r="C30" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="48">
@@ -3452,601 +3221,601 @@
         <v>5</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="24">
       <c r="A32" s="28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="48">
       <c r="A33" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>35</v>
-      </c>
       <c r="C33" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H33" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="48">
       <c r="A34" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="C34" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H34" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="72">
       <c r="A35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>40</v>
-      </c>
       <c r="C35" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H35" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="72">
       <c r="A36" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>42</v>
-      </c>
       <c r="C36" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H36" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I36" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="48">
       <c r="A37" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="C37" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="48">
       <c r="A38" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>46</v>
-      </c>
       <c r="C38" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I38" s="13"/>
     </row>
     <row r="39" spans="1:9" ht="60">
       <c r="A39" s="24" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" ht="60">
       <c r="A40" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="25" t="s">
-        <v>49</v>
-      </c>
       <c r="C40" s="25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:9" ht="48">
       <c r="A41" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="C41" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I41" s="13"/>
     </row>
     <row r="42" spans="1:9" ht="48">
       <c r="A42" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>53</v>
-      </c>
       <c r="C42" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H42" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="48">
       <c r="A43" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>55</v>
-      </c>
       <c r="C43" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="24">
       <c r="A44" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>57</v>
-      </c>
       <c r="C44" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I44" s="13"/>
     </row>
     <row r="45" spans="1:9" ht="48">
       <c r="A45" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I45" s="13"/>
     </row>
     <row r="46" spans="1:9" ht="48">
       <c r="A46" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>61</v>
-      </c>
       <c r="C46" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I46" s="13"/>
     </row>
     <row r="47" spans="1:9" ht="48">
       <c r="A47" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>63</v>
-      </c>
       <c r="C47" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I47" s="13"/>
     </row>
     <row r="48" spans="1:9" ht="48">
       <c r="A48" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I48" s="13"/>
     </row>
     <row r="49" spans="1:9" ht="48">
       <c r="A49" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>66</v>
-      </c>
       <c r="C49" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I49" s="13"/>
     </row>
     <row r="50" spans="1:9" ht="48">
       <c r="A50" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>68</v>
-      </c>
       <c r="C50" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I50" s="13"/>
     </row>
     <row r="51" spans="1:9" ht="48">
       <c r="A51" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I51" s="13"/>
     </row>
     <row r="52" spans="1:9" ht="48">
       <c r="A52" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="14" t="s">
-        <v>71</v>
-      </c>
       <c r="C52" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I52" s="13"/>
     </row>
     <row r="53" spans="1:9" ht="48">
       <c r="A53" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B53" s="14" t="s">
-        <v>73</v>
-      </c>
       <c r="C53" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I53" s="13"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="13" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
     </row>
     <row r="55" spans="1:9" ht="24">
       <c r="A55" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G56" s="17"/>
       <c r="H56" s="17"/>
@@ -4054,37 +3823,37 @@
     </row>
     <row r="57" spans="1:9" ht="72">
       <c r="A57" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="18"/>
       <c r="F58" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
@@ -4092,176 +3861,176 @@
     </row>
     <row r="59" spans="1:9" ht="36">
       <c r="A59" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24">
       <c r="A60" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="14"/>
       <c r="E61" s="14"/>
       <c r="F61" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="24">
       <c r="A62" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>181</v>
-      </c>
       <c r="C62" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="14"/>
       <c r="F62" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="24">
       <c r="A64" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B64" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="C64" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D64" s="14"/>
       <c r="E64" s="14"/>
       <c r="F64" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
     </row>
     <row r="65" spans="1:9" ht="48">
       <c r="A65" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
       <c r="F65" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="24">
       <c r="A66" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
@@ -4269,62 +4038,62 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
@@ -4332,16 +4101,16 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18"/>
       <c r="F71" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G71" s="19"/>
       <c r="H71" s="19"/>
@@ -4349,16 +4118,16 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
       <c r="F72" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G72" s="19"/>
       <c r="H72" s="19"/>
@@ -4366,16 +4135,16 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="19" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G73" s="19"/>
       <c r="H73" s="19"/>
@@ -4383,16 +4152,16 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G74" s="19"/>
       <c r="H74" s="19"/>
@@ -4400,16 +4169,16 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G75" s="19"/>
       <c r="H75" s="19"/>
@@ -4417,189 +4186,189 @@
     </row>
     <row r="76" spans="1:9" ht="24">
       <c r="A76" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14"/>
       <c r="F76" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H76" s="10"/>
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="1:9" ht="36">
       <c r="A77" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D77" s="14"/>
       <c r="E77" s="14"/>
       <c r="F77" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D78" s="14"/>
       <c r="E78" s="14"/>
       <c r="F78" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="24">
       <c r="A79" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="24">
       <c r="A80" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D80" s="14"/>
       <c r="E80" s="14"/>
       <c r="F80" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="24">
       <c r="A81" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D81" s="14"/>
       <c r="E81" s="14"/>
       <c r="F81" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="24">
       <c r="A82" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D84" s="14"/>
       <c r="E84" s="14"/>
       <c r="F84" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D85" s="18"/>
       <c r="E85" s="18"/>
       <c r="F85" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G85" s="19"/>
       <c r="H85" s="19"/>
@@ -4607,35 +4376,35 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D87" s="18"/>
       <c r="E87" s="18"/>
       <c r="F87" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G87" s="19"/>
       <c r="H87" s="19"/>
@@ -4643,16 +4412,16 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D88" s="18"/>
       <c r="E88" s="18"/>
       <c r="F88" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G88" s="19"/>
       <c r="H88" s="19"/>
@@ -4660,16 +4429,16 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="18"/>
       <c r="E89" s="18"/>
       <c r="F89" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G89" s="19"/>
       <c r="H89" s="19"/>
@@ -4677,16 +4446,16 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="18"/>
       <c r="F90" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G90" s="19"/>
       <c r="H90" s="19"/>
@@ -4694,16 +4463,16 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D91" s="18"/>
       <c r="E91" s="18"/>
       <c r="F91" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G91" s="19"/>
       <c r="H91" s="19"/>
@@ -4711,16 +4480,16 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G92" s="19"/>
       <c r="H92" s="19"/>
@@ -4728,16 +4497,16 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D93" s="18"/>
       <c r="E93" s="18"/>
       <c r="F93" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G93" s="19"/>
       <c r="H93" s="19"/>
@@ -4745,16 +4514,16 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D94" s="18"/>
       <c r="E94" s="18"/>
       <c r="F94" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G94" s="19"/>
       <c r="H94" s="19"/>
@@ -4762,16 +4531,16 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G95" s="19"/>
       <c r="H95" s="19"/>
@@ -4779,16 +4548,16 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G96" s="19"/>
       <c r="H96" s="19"/>
@@ -4796,16 +4565,16 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G97" s="19"/>
       <c r="H97" s="19"/>
@@ -4813,96 +4582,96 @@
     </row>
     <row r="98" spans="1:9" ht="48">
       <c r="A98" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60">
       <c r="A99" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="48">
       <c r="A100" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G101" s="19"/>
       <c r="H101" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I101" s="19"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G102" s="19"/>
       <c r="H102" s="19"/>
@@ -4910,18 +4679,18 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>249</v>
-      </c>
-      <c r="B103" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>251</v>
       </c>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G103" s="19"/>
       <c r="H103" s="19"/>
@@ -4929,18 +4698,18 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B104" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G104" s="19"/>
       <c r="H104" s="19"/>
@@ -4948,78 +4717,78 @@
     </row>
     <row r="105" spans="1:9" ht="24">
       <c r="A105" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="48">
       <c r="A106" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="24">
       <c r="A108" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="109" spans="1:9">

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="325">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1683,20 +1683,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>name：索引名
-indexdef：索引键
-unique：索引是否唯一
-enforced：索引是否强制唯一
-flag：是否离线索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>collectionname：表名
-indexname：索引名、
-oid：索引记录的oid</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>collectionname：表名
 indexname：索引名、
 oid：索引记录的oid</t>
@@ -1868,6 +1854,45 @@
 subclname：子分区集合全名
 lowbound：开始范围
 upbound：结束范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.56:8000/?cmd=attach collection&amp;collectionname=cs.cl&amp;subclname=cs.cl1&amp;lowbound={age:0}&amp;upbound={age:20}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.56:8000/?cmd=create index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl&amp;indexdef={a:1}&amp;unique=true&amp;enforced=true&amp;flag=offline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>name：索引名
+indexdef：索引键
+unique：索引是否唯一(可选，默认false)
+enforced：索引是否强制唯一(可选，默认false)
+flag：是否离线索引(可选，默认online，online/offline)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.56:8000/?cmd=drop index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">collectionname：表名
+indexname：索引名、
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oid：索引记录的oid（暂时没实现通过oid删除索引）</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2514,12 +2539,12 @@
     </row>
     <row r="2" spans="1:1" ht="27">
       <c r="A2" s="38" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2765,7 +2790,7 @@
         <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>108</v>
@@ -2871,7 +2896,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2897,7 +2925,7 @@
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
     </row>
-    <row r="15" spans="1:9" ht="60">
+    <row r="15" spans="1:9" ht="96">
       <c r="A15" s="3" t="s">
         <v>215</v>
       </c>
@@ -2910,10 +2938,13 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>296</v>
+        <v>322</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="24">
@@ -3007,7 +3038,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="12" customFormat="1" ht="36">
+    <row r="21" spans="1:9" s="12" customFormat="1" ht="48">
       <c r="A21" s="3" t="s">
         <v>221</v>
       </c>
@@ -3020,12 +3051,14 @@
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="H21" s="3"/>
+        <v>324</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" s="12" customFormat="1" ht="36">
@@ -3042,7 +3075,7 @@
         <v>133</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -3077,10 +3110,10 @@
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3135,7 +3168,7 @@
         <v>133</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="36">
@@ -3154,7 +3187,7 @@
         <v>92</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>96</v>
@@ -3179,7 +3212,7 @@
         <v>92</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>97</v>
@@ -3229,7 +3262,7 @@
         <v>87</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>93</v>
@@ -3240,7 +3273,7 @@
     </row>
     <row r="32" spans="1:9" ht="24">
       <c r="A32" s="28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>31</v>
@@ -3413,7 +3446,7 @@
     </row>
     <row r="39" spans="1:9" ht="60">
       <c r="A39" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>46</v>
@@ -3762,7 +3795,7 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>169</v>
@@ -3875,7 +3908,7 @@
         <v>133</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24">
@@ -3894,7 +3927,7 @@
         <v>133</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4008,7 +4041,7 @@
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>133</v>
@@ -4027,7 +4060,7 @@
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F67" s="20" t="s">
         <v>133</v>
@@ -4048,7 +4081,7 @@
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>133</v>
@@ -4066,14 +4099,14 @@
         <v>77</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="19"/>
@@ -4083,13 +4116,13 @@
         <v>150</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>77</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="20" t="s">
@@ -4118,7 +4151,7 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="18" t="s">
@@ -4135,7 +4168,7 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="19" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="18" t="s">
@@ -4354,7 +4387,7 @@
         <v>133</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:9">

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -73,7 +73,8 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>，数字和字符串两种格式</t>
+          <t>，数字和字符串两种格式
+后续版本新增的命令，参数名采用括号内名字。逐渐替换掉旧的名字</t>
         </r>
       </text>
     </comment>
@@ -404,7 +405,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="327">
   <si>
     <t>命令</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -462,16 +463,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-sort: 排序字段名
-selector: 查询结果列
-skip：跳过多少行
-returnnum：最大返回条数
-filter：查询条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>queryandupdate</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -552,13 +543,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-sort: 排序字段名
-selector: 查询结果列
-filter：查询条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>list contexts current</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -643,11 +627,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字
-name：表名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>snapshot contexts</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -773,11 +752,6 @@
   </si>
   <si>
     <t>创建表空间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cs名字</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1341,10 +1315,6 @@
   </si>
   <si>
     <t>从主分区集合中分离出子分区集合</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>subclname：子分区集合全名</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1541,54 +1511,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-sort: 排序字段名
-selector: 查询结果列
-skip：跳过多少行
-returnnum：最大返回条数
-filter：查询条件
-hint:指定索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字;
-updator: 更新操作
-sort: 排序字段名
-selector: 查询结果列
-skip：跳过多少行
-returnnum：最大返回条数
-filter：查询条件
-returnnew:是否返回更新后记录
-hint:指定索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cmd：命令字; 
-name：cl名字; 
-source: 源数据组;
-target: 目标数据组;
-splitpercent: 百分比
-splitquery: 条件
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isasync：是否异步</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>alter domain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1622,12 +1544,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-insertor: 待插入数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数据操作</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1636,38 +1552,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-deletor: 删除条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-updator: 更新操作
-filter:更新条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-updator: 更新操作
-filter:更新条件
-setoninsert:插入数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>业务监控</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>元数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-options: 属性</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1696,69 +1585,6 @@
   </si>
   <si>
     <t>collectionname:表名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cmd：命令字; 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>name：cl名字;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 
-options: 选项(可选参数)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">cmd：命令字; 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>name：cl名字;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-csname/collectionspacename：cs名字
-options:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1842,13 +1668,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-matcher:条件;
-hint:指定索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>cmd:命令字
 collectionname：主表名字；
 subclname：子分区集合全名
@@ -1862,14 +1681,6 @@
   </si>
   <si>
     <t>http://192.168.20.56:8000/?cmd=create index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl&amp;indexdef={a:1}&amp;unique=true&amp;enforced=true&amp;flag=offline</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>name：索引名
-indexdef：索引键
-unique：索引是否唯一(可选，默认false)
-enforced：索引是否强制唯一(可选，默认false)
-flag：是否离线索引(可选，默认online，online/offline)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1895,12 +1706,421 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>cmd：命令字; 
+name(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collectionname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：cl名字; 
+insertor: 待插入数据</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>cmd：命令字; 
+name(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collectionname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：cl名字;
+updator: 更新操作
+sort(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orderby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>): 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：最大返回条数
+filter(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Matcher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：查询条件
+returnnew:是否返回更新后记录
+hint:指定索引</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+sort(Orderby): 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum(Limit)：最大返回条数
+filter(Matcher)：查询条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+deletor(Matcher): 删除条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+updator: 更新操作
+filter(Matcher):更新条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+updator: 更新操作
+filter(Matcher):更新条件
+setoninsert:插入数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+matcher:条件;
+hint:指定索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionname)：cl名字; 
+options: 属性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cmd：命令字; 
+name(Collectionname)：cl名字; 
+source: 源数据组;
+target: 目标数据组;
+splitpercent: 百分比
+splitquery(Lowbound): 起始条件
+SplitEndQuery(Upbound):结束条件
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isasync：是否异步</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cmd：命令字;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name(collectionname)：cl名字;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+options: 选项(可选参数)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cmd：命令字; 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name(collectionname)：cl名字;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionspace)：cs名字</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionspace)：cs名字
+options:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+sort(Orderby): 排序字段名
+selector: 查询结果列
+filter(Matcher)：查询条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+sort(Orderby): 排序字段名
+selector: 查询结果列
+filter：查询条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字
+name(Collectionname)：表名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd:命令字
+collectionname：主表名字；subclname：子分区集合全名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd:命令字
+collectionname：表名
+indexname：索引名
+indexdef：索引键
+unique：索引是否唯一(可选，默认false)
+enforced：索引是否强制唯一(可选，默认false)
+flag：是否离线索引(可选，默认online，online/offline)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>cmd：命令字; 
+name(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collectionname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：cl名字; 
+sort(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orderby</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>): 排序字段名 
+selector: 查询结果列
+skip：跳过多少行
+returnnum(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：最大返回条数
+filter(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Matcher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)：查询条件
+hint:指定索引</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.56:8000/?cmd=list indexes&amp;collectionname=cs.cl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1985,6 +2205,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2534,17 +2763,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="27">
       <c r="A2" s="38" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2576,16 +2805,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>2</v>
@@ -2603,23 +2832,23 @@
         <v>11</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="96">
@@ -2630,337 +2859,337 @@
         <v>13</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="120">
       <c r="A4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>16</v>
-      </c>
       <c r="C4" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="84">
       <c r="A5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36">
       <c r="A6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>20</v>
-      </c>
       <c r="C6" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48">
       <c r="A7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60">
       <c r="A8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="48">
       <c r="A9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="36">
       <c r="A10" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>314</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="96">
+      <c r="A11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="28" t="s">
+      <c r="B11" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="84">
-      <c r="A11" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>98</v>
-      </c>
       <c r="D11" s="26" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60">
       <c r="A13" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="32" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="34" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
     </row>
-    <row r="15" spans="1:9" ht="96">
+    <row r="15" spans="1:9" ht="120">
       <c r="A15" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="24">
       <c r="A16" s="19" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="19"/>
@@ -2968,47 +3197,47 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="48">
       <c r="A18" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>233</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="32" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -3019,79 +3248,79 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="12" customFormat="1" ht="48">
       <c r="A21" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" s="12" customFormat="1" ht="36">
       <c r="A22" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="36" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="19" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="19"/>
@@ -3099,54 +3328,57 @@
     </row>
     <row r="24" spans="1:9" ht="36">
       <c r="A24" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>297</v>
+        <v>284</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="19" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="19"/>
@@ -3154,21 +3386,21 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="36">
@@ -3179,21 +3411,21 @@
         <v>7</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="H28" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="I28" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="24">
@@ -3204,49 +3436,49 @@
         <v>9</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="48">
       <c r="A30" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>90</v>
+        <v>318</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="48">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="36">
       <c r="A31" s="13" t="s">
         <v>4</v>
       </c>
@@ -3254,601 +3486,601 @@
         <v>5</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="24">
       <c r="A32" s="28" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="48">
       <c r="A33" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>34</v>
-      </c>
       <c r="C33" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="48">
       <c r="A34" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="72">
       <c r="A35" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="72">
       <c r="A36" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="48">
       <c r="A37" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="48">
       <c r="A38" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I38" s="13"/>
     </row>
     <row r="39" spans="1:9" ht="60">
       <c r="A39" s="24" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" ht="60">
       <c r="A40" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:9" ht="48">
       <c r="A41" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I41" s="13"/>
     </row>
     <row r="42" spans="1:9" ht="48">
       <c r="A42" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="48">
       <c r="A43" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="24">
       <c r="A44" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I44" s="13"/>
     </row>
     <row r="45" spans="1:9" ht="48">
       <c r="A45" s="13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I45" s="13"/>
     </row>
     <row r="46" spans="1:9" ht="48">
       <c r="A46" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I46" s="13"/>
     </row>
     <row r="47" spans="1:9" ht="48">
       <c r="A47" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I47" s="13"/>
     </row>
     <row r="48" spans="1:9" ht="48">
       <c r="A48" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I48" s="13"/>
     </row>
     <row r="49" spans="1:9" ht="48">
       <c r="A49" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I49" s="13"/>
     </row>
     <row r="50" spans="1:9" ht="48">
       <c r="A50" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I50" s="13"/>
     </row>
     <row r="51" spans="1:9" ht="48">
       <c r="A51" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>35</v>
+        <v>321</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I51" s="13"/>
     </row>
     <row r="52" spans="1:9" ht="48">
       <c r="A52" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I52" s="13"/>
     </row>
     <row r="53" spans="1:9" ht="48">
       <c r="A53" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I53" s="13"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
     </row>
     <row r="55" spans="1:9" ht="24">
       <c r="A55" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G56" s="17"/>
       <c r="H56" s="17"/>
@@ -3856,37 +4088,37 @@
     </row>
     <row r="57" spans="1:9" ht="72">
       <c r="A57" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="18"/>
       <c r="F58" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
@@ -3894,176 +4126,176 @@
     </row>
     <row r="59" spans="1:9" ht="36">
       <c r="A59" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24">
       <c r="A60" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D61" s="14"/>
       <c r="E61" s="14"/>
       <c r="F61" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="24">
       <c r="A62" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="14"/>
       <c r="F62" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="24">
       <c r="A64" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D64" s="14"/>
       <c r="E64" s="14"/>
       <c r="F64" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
     </row>
     <row r="65" spans="1:9" ht="48">
       <c r="A65" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
       <c r="F65" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="24">
       <c r="A66" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
@@ -4071,62 +4303,62 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
@@ -4134,16 +4366,16 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18"/>
       <c r="F71" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G71" s="19"/>
       <c r="H71" s="19"/>
@@ -4151,16 +4383,16 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="19" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
       <c r="F72" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G72" s="19"/>
       <c r="H72" s="19"/>
@@ -4168,16 +4400,16 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="19" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G73" s="19"/>
       <c r="H73" s="19"/>
@@ -4185,16 +4417,16 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G74" s="19"/>
       <c r="H74" s="19"/>
@@ -4202,16 +4434,16 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G75" s="19"/>
       <c r="H75" s="19"/>
@@ -4219,189 +4451,189 @@
     </row>
     <row r="76" spans="1:9" ht="24">
       <c r="A76" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14"/>
       <c r="F76" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H76" s="10"/>
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="1:9" ht="36">
       <c r="A77" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D77" s="14"/>
       <c r="E77" s="14"/>
       <c r="F77" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D78" s="14"/>
       <c r="E78" s="14"/>
       <c r="F78" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="24">
       <c r="A79" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="24">
       <c r="A80" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D80" s="14"/>
       <c r="E80" s="14"/>
       <c r="F80" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="24">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D81" s="14"/>
       <c r="E81" s="14"/>
       <c r="F81" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="24">
       <c r="A82" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D84" s="14"/>
       <c r="E84" s="14"/>
       <c r="F84" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="19" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D85" s="18"/>
       <c r="E85" s="18"/>
       <c r="F85" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G85" s="19"/>
       <c r="H85" s="19"/>
@@ -4409,35 +4641,35 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D87" s="18"/>
       <c r="E87" s="18"/>
       <c r="F87" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G87" s="19"/>
       <c r="H87" s="19"/>
@@ -4445,16 +4677,16 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="19" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D88" s="18"/>
       <c r="E88" s="18"/>
       <c r="F88" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G88" s="19"/>
       <c r="H88" s="19"/>
@@ -4462,16 +4694,16 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D89" s="18"/>
       <c r="E89" s="18"/>
       <c r="F89" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G89" s="19"/>
       <c r="H89" s="19"/>
@@ -4479,16 +4711,16 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="18"/>
       <c r="F90" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G90" s="19"/>
       <c r="H90" s="19"/>
@@ -4496,16 +4728,16 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D91" s="18"/>
       <c r="E91" s="18"/>
       <c r="F91" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G91" s="19"/>
       <c r="H91" s="19"/>
@@ -4513,16 +4745,16 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G92" s="19"/>
       <c r="H92" s="19"/>
@@ -4530,16 +4762,16 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="19" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D93" s="18"/>
       <c r="E93" s="18"/>
       <c r="F93" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G93" s="19"/>
       <c r="H93" s="19"/>
@@ -4547,16 +4779,16 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D94" s="18"/>
       <c r="E94" s="18"/>
       <c r="F94" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G94" s="19"/>
       <c r="H94" s="19"/>
@@ -4564,16 +4796,16 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="19" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G95" s="19"/>
       <c r="H95" s="19"/>
@@ -4581,16 +4813,16 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="19" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G96" s="19"/>
       <c r="H96" s="19"/>
@@ -4598,16 +4830,16 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="19" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G97" s="19"/>
       <c r="H97" s="19"/>
@@ -4615,96 +4847,96 @@
     </row>
     <row r="98" spans="1:9" ht="48">
       <c r="A98" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60">
       <c r="A99" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="48">
       <c r="A100" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G101" s="19"/>
       <c r="H101" s="19" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I101" s="19"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="19" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G102" s="19"/>
       <c r="H102" s="19"/>
@@ -4712,18 +4944,18 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="19" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G103" s="19"/>
       <c r="H103" s="19"/>
@@ -4731,18 +4963,18 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="19" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B104" s="20" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G104" s="19"/>
       <c r="H104" s="19"/>
@@ -4750,78 +4982,78 @@
     </row>
     <row r="105" spans="1:9" ht="24">
       <c r="A105" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="48">
       <c r="A106" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="24">
       <c r="A108" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:9">

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -1680,10 +1680,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>http://192.168.20.56:8000/?cmd=create index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl&amp;indexdef={a:1}&amp;unique=true&amp;enforced=true&amp;flag=offline</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>http://192.168.20.56:8000/?cmd=drop index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2001,16 +1997,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cmd:命令字
-collectionname：表名
-indexname：索引名
-indexdef：索引键
-unique：索引是否唯一(可选，默认false)
-enforced：索引是否强制唯一(可选，默认false)
-flag：是否离线索引(可选，默认online，online/offline)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>cmd：命令字; 
 name(</t>
@@ -2113,6 +2099,20 @@
   </si>
   <si>
     <t>http://192.168.20.56:8000/?cmd=list indexes&amp;collectionname=cs.cl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd:命令字
+collectionname：表名
+indexname：索引名
+indexdef：索引键
+unique：索引是否唯一(可选，默认false)
+enforced：索引是否强制唯一(可选，默认false)
+SortBufferSize：索引排序的大小(单位MB)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://192.168.20.56:8000/?cmd=create index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl&amp;indexdef={a:1}&amp;unique=true&amp;enforced=true</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2842,7 +2842,7 @@
         <v>88</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>95</v>
@@ -2867,7 +2867,7 @@
         <v>88</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>96</v>
@@ -2892,7 +2892,7 @@
         <v>88</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>98</v>
@@ -2917,7 +2917,7 @@
         <v>88</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>100</v>
@@ -2942,7 +2942,7 @@
         <v>88</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>101</v>
@@ -2967,7 +2967,7 @@
         <v>88</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>102</v>
@@ -2992,7 +2992,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>103</v>
@@ -3019,7 +3019,7 @@
         <v>88</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>104</v>
@@ -3048,7 +3048,7 @@
         <v>88</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H10" s="28" t="s">
         <v>106</v>
@@ -3075,7 +3075,7 @@
         <v>88</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>107</v>
@@ -3170,10 +3170,10 @@
         <v>84</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="24">
@@ -3232,7 +3232,7 @@
         <v>129</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3283,10 +3283,10 @@
         <v>84</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I21" s="3"/>
     </row>
@@ -3345,7 +3345,7 @@
         <v>284</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3419,7 +3419,7 @@
         <v>88</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>92</v>
@@ -3444,7 +3444,7 @@
         <v>88</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>93</v>
@@ -3469,7 +3469,7 @@
         <v>84</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>73</v>
@@ -3494,7 +3494,7 @@
         <v>84</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>89</v>
@@ -3544,7 +3544,7 @@
         <v>88</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>109</v>
@@ -3569,7 +3569,7 @@
         <v>88</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>111</v>
@@ -3594,7 +3594,7 @@
         <v>88</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>113</v>
@@ -3619,7 +3619,7 @@
         <v>88</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>115</v>
@@ -3644,7 +3644,7 @@
         <v>88</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>117</v>
@@ -3669,7 +3669,7 @@
         <v>88</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>118</v>
@@ -3738,7 +3738,7 @@
         <v>88</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>76</v>
@@ -3761,7 +3761,7 @@
         <v>88</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>121</v>
@@ -3786,7 +3786,7 @@
         <v>88</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>77</v>
@@ -3811,7 +3811,7 @@
         <v>88</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>78</v>
@@ -3834,7 +3834,7 @@
         <v>88</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>79</v>
@@ -3857,7 +3857,7 @@
         <v>88</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>80</v>
@@ -3880,7 +3880,7 @@
         <v>88</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>124</v>
@@ -3903,7 +3903,7 @@
         <v>88</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>81</v>
@@ -3926,7 +3926,7 @@
         <v>88</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>125</v>
@@ -3949,7 +3949,7 @@
         <v>88</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>126</v>
@@ -3972,7 +3972,7 @@
         <v>88</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>82</v>
@@ -3995,7 +3995,7 @@
         <v>88</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>127</v>
@@ -4018,7 +4018,7 @@
         <v>88</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>128</v>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -1963,17 +1963,6 @@
   </si>
   <si>
     <t>cmd：命令字; 
-name(Collectionspace)：cs名字</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name(Collectionspace)：cs名字
-options:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
 sort(Orderby): 排序字段名
 selector: 查询结果列
 filter(Matcher)：查询条件</t>
@@ -2113,6 +2102,18 @@
   </si>
   <si>
     <t>http://192.168.20.56:8000/?cmd=create index&amp;collectionname=cs.cl&amp;indexname=idx_cs_cl&amp;indexdef={a:1}&amp;unique=true&amp;enforced=true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">cmd：命令字; 
+name(Collectionspace)：cs名字
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name(Collectionspace)：cs名字
+options:集合空间可选属性。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2867,7 +2868,7 @@
         <v>88</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>96</v>
@@ -3170,10 +3171,10 @@
         <v>84</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="24">
@@ -3232,7 +3233,7 @@
         <v>129</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3345,7 +3346,7 @@
         <v>284</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3469,7 +3470,7 @@
         <v>84</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>73</v>
@@ -3494,7 +3495,7 @@
         <v>84</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>89</v>
@@ -3544,7 +3545,7 @@
         <v>88</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>109</v>
@@ -3569,7 +3570,7 @@
         <v>88</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>111</v>
@@ -3594,7 +3595,7 @@
         <v>88</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>113</v>
@@ -3619,7 +3620,7 @@
         <v>88</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>115</v>
@@ -3644,7 +3645,7 @@
         <v>88</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>117</v>
@@ -3669,7 +3670,7 @@
         <v>88</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>118</v>
@@ -3738,7 +3739,7 @@
         <v>88</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>76</v>
@@ -3761,7 +3762,7 @@
         <v>88</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>121</v>
@@ -3786,7 +3787,7 @@
         <v>88</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>77</v>
@@ -3811,7 +3812,7 @@
         <v>88</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>78</v>
@@ -3834,7 +3835,7 @@
         <v>88</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>79</v>
@@ -3857,7 +3858,7 @@
         <v>88</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>80</v>
@@ -3880,7 +3881,7 @@
         <v>88</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>124</v>
@@ -3903,7 +3904,7 @@
         <v>88</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>81</v>
@@ -3926,7 +3927,7 @@
         <v>88</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>125</v>
@@ -3949,7 +3950,7 @@
         <v>88</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>126</v>
@@ -3972,7 +3973,7 @@
         <v>88</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>82</v>
@@ -3995,7 +3996,7 @@
         <v>88</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>127</v>
@@ -4018,7 +4019,7 @@
         <v>88</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>128</v>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -4277,7 +4277,7 @@
         <v>291</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>184</v>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332">
   <si>
     <t>1.用户必须已经登陆OM</t>
   </si>
@@ -1296,18 +1296,15 @@
   <si>
     <t>sessionid：
 options: {
-  HostName: (待实现)
-  ServiceName: (待实现)
-  NodeID: (待实现)
-  GroupName: (待实现)
-  GroupID: (待实现)
+  HostName:
+  svcame:
+  NodeID: 
+  GroupName: 
+  GroupID: 
 }</t>
   </si>
   <si>
-    <t>现在只能force coord的session，要拿到coord的session要带条件{ Global: false }</t>
-  </si>
-  <si>
-    <t>需要等许导实现更多功能</t>
+    <t>cmd=force session&amp;SessionID=22&amp;Options={ "HostName": "ubuntu-dev12", "svcname": "42000"  }</t>
   </si>
   <si>
     <t>force stepup</t>
@@ -1591,12 +1588,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1619,13 +1616,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1716,30 +1706,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -1764,6 +1730,30 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1930,24 +1920,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2009,6 +1981,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2141,26 +2131,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2184,6 +2154,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2192,10 +2182,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2204,138 +2194,138 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -2402,7 +2392,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2411,27 +2400,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2789,7 +2768,7 @@
       </c>
     </row>
     <row r="2" ht="27" spans="1:1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2806,8 +2785,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:K110"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.5833333333333" style="2" customWidth="1"/>
@@ -2846,12 +2825,12 @@
       <c r="H1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="48" spans="1:9">
+    <row r="2" ht="48" hidden="1" spans="1:9">
       <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
@@ -2878,7 +2857,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="144" spans="1:9">
+    <row r="3" ht="144" hidden="1" spans="1:9">
       <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
@@ -2903,7 +2882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="180" spans="1:9">
+    <row r="4" ht="180" hidden="1" spans="1:9">
       <c r="A4" s="9" t="s">
         <v>25</v>
       </c>
@@ -2928,7 +2907,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" ht="108" spans="1:9">
+    <row r="5" ht="108" hidden="1" spans="1:9">
       <c r="A5" s="9" t="s">
         <v>30</v>
       </c>
@@ -2953,7 +2932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="60" spans="1:9">
+    <row r="6" ht="60" hidden="1" spans="1:9">
       <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
@@ -2978,7 +2957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="60" spans="1:9">
+    <row r="7" ht="60" hidden="1" spans="1:9">
       <c r="A7" s="9" t="s">
         <v>38</v>
       </c>
@@ -3003,7 +2982,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" ht="72" spans="1:9">
+    <row r="8" ht="72" hidden="1" spans="1:9">
       <c r="A8" s="9" t="s">
         <v>42</v>
       </c>
@@ -3028,7 +3007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="60" spans="1:9">
+    <row r="9" ht="60" hidden="1" spans="1:9">
       <c r="A9" s="9" t="s">
         <v>46</v>
       </c>
@@ -3055,7 +3034,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:9">
+    <row r="10" ht="72" hidden="1" spans="1:9">
       <c r="A10" s="13" t="s">
         <v>52</v>
       </c>
@@ -3084,7 +3063,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="132" spans="1:9">
+    <row r="11" ht="132" hidden="1" spans="1:9">
       <c r="A11" s="17" t="s">
         <v>58</v>
       </c>
@@ -3111,7 +3090,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12" s="4" t="s">
         <v>62</v>
       </c>
@@ -3132,7 +3111,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" ht="72" spans="1:8">
+    <row r="13" ht="72" hidden="1" spans="1:8">
       <c r="A13" s="4" t="s">
         <v>67</v>
       </c>
@@ -3158,7 +3137,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" hidden="1" spans="1:9">
       <c r="A14" s="24" t="s">
         <v>71</v>
       </c>
@@ -3181,7 +3160,7 @@
       <c r="H14" s="24"/>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="120" spans="1:8">
+    <row r="15" ht="120" hidden="1" spans="1:8">
       <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
@@ -3203,7 +3182,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" hidden="1" spans="1:9">
       <c r="A16" s="28" t="s">
         <v>78</v>
       </c>
@@ -3222,7 +3201,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" s="4" t="s">
         <v>80</v>
       </c>
@@ -3255,7 +3234,7 @@
       <c r="E18" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="23" t="s">
@@ -3264,12 +3243,12 @@
       <c r="H18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J18" s="43" t="s">
+      <c r="J18" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K18" s="44"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="K18" s="39"/>
+    </row>
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" s="24" t="s">
         <v>88</v>
       </c>
@@ -3280,7 +3259,7 @@
       <c r="F19" s="22"/>
       <c r="G19" s="23"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" s="4" t="s">
         <v>89</v>
       </c>
@@ -3301,7 +3280,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="48" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="48" hidden="1" spans="1:9">
       <c r="A21" s="4" t="s">
         <v>92</v>
       </c>
@@ -3324,26 +3303,26 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="36" spans="1:9">
-      <c r="A22" s="33" t="s">
+    <row r="22" s="1" customFormat="1" ht="36" hidden="1" spans="1:9">
+      <c r="A22" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="36" t="s">
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+    </row>
+    <row r="23" hidden="1" spans="1:9">
       <c r="A23" s="28" t="s">
         <v>98</v>
       </c>
@@ -3360,7 +3339,7 @@
       <c r="H23" s="28"/>
       <c r="I23" s="28"/>
     </row>
-    <row r="24" ht="36" spans="1:8">
+    <row r="24" ht="36" hidden="1" spans="1:8">
       <c r="A24" s="4" t="s">
         <v>99</v>
       </c>
@@ -3382,7 +3361,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" ht="84" spans="1:10">
+    <row r="25" ht="84" hidden="1" spans="1:10">
       <c r="A25" s="4" t="s">
         <v>103</v>
       </c>
@@ -3397,17 +3376,17 @@
       <c r="F25" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="23" t="s">
         <v>105</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J25" s="43" t="s">
+      <c r="J25" s="39" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" hidden="1" spans="1:9">
       <c r="A26" s="28" t="s">
         <v>108</v>
       </c>
@@ -3425,7 +3404,7 @@
       <c r="I26" s="28"/>
     </row>
     <row r="27" ht="24" spans="1:11">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B27" s="21" t="s">
@@ -3436,7 +3415,7 @@
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="23" t="s">
@@ -3445,12 +3424,12 @@
       <c r="H27" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J27" s="43" t="s">
+      <c r="J27" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K27" s="44"/>
-    </row>
-    <row r="28" ht="60" spans="1:9">
+      <c r="K27" s="39"/>
+    </row>
+    <row r="28" ht="60" hidden="1" spans="1:9">
       <c r="A28" s="9" t="s">
         <v>113</v>
       </c>
@@ -3475,7 +3454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" ht="36" spans="1:9">
+    <row r="29" ht="36" hidden="1" spans="1:9">
       <c r="A29" s="9" t="s">
         <v>118</v>
       </c>
@@ -3500,7 +3479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" ht="96" spans="1:9">
+    <row r="30" ht="96" hidden="1" spans="1:9">
       <c r="A30" s="9" t="s">
         <v>122</v>
       </c>
@@ -3525,7 +3504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" ht="48" spans="1:9">
+    <row r="31" ht="48" hidden="1" spans="1:9">
       <c r="A31" s="9" t="s">
         <v>127</v>
       </c>
@@ -3550,7 +3529,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" ht="36" spans="1:9">
+    <row r="32" ht="36" hidden="1" spans="1:9">
       <c r="A32" s="13" t="s">
         <v>131</v>
       </c>
@@ -3575,7 +3554,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" ht="48" spans="1:9">
+    <row r="33" ht="48" hidden="1" spans="1:9">
       <c r="A33" s="9" t="s">
         <v>136</v>
       </c>
@@ -3600,7 +3579,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" ht="48" spans="1:9">
+    <row r="34" ht="48" hidden="1" spans="1:9">
       <c r="A34" s="9" t="s">
         <v>141</v>
       </c>
@@ -3625,7 +3604,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" ht="60" spans="1:9">
+    <row r="35" ht="60" hidden="1" spans="1:9">
       <c r="A35" s="9" t="s">
         <v>145</v>
       </c>
@@ -3650,7 +3629,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" ht="72" spans="1:9">
+    <row r="36" ht="72" hidden="1" spans="1:9">
       <c r="A36" s="9" t="s">
         <v>149</v>
       </c>
@@ -3675,7 +3654,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" ht="48" spans="1:9">
+    <row r="37" ht="48" hidden="1" spans="1:9">
       <c r="A37" s="9" t="s">
         <v>153</v>
       </c>
@@ -3700,7 +3679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" ht="48" spans="1:9">
+    <row r="38" ht="48" hidden="1" spans="1:9">
       <c r="A38" s="9" t="s">
         <v>156</v>
       </c>
@@ -3745,7 +3724,7 @@
         <v>163</v>
       </c>
       <c r="I39" s="17"/>
-      <c r="J39" s="43" t="s">
+      <c r="J39" s="39" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3771,11 +3750,11 @@
         <v>166</v>
       </c>
       <c r="I40" s="17"/>
-      <c r="J40" s="43" t="s">
+      <c r="J40" s="39" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" ht="48" spans="1:9">
+    <row r="41" ht="48" hidden="1" spans="1:9">
       <c r="A41" s="9" t="s">
         <v>167</v>
       </c>
@@ -3798,7 +3777,7 @@
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" ht="48" spans="1:9">
+    <row r="42" ht="48" hidden="1" spans="1:9">
       <c r="A42" s="9" t="s">
         <v>170</v>
       </c>
@@ -3823,7 +3802,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" ht="48" spans="1:9">
+    <row r="43" ht="48" hidden="1" spans="1:9">
       <c r="A43" s="9" t="s">
         <v>174</v>
       </c>
@@ -3848,7 +3827,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="44" ht="36" spans="1:9">
+    <row r="44" ht="36" hidden="1" spans="1:9">
       <c r="A44" s="9" t="s">
         <v>103</v>
       </c>
@@ -3871,7 +3850,7 @@
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" ht="48" spans="1:9">
+    <row r="45" ht="48" hidden="1" spans="1:9">
       <c r="A45" s="9" t="s">
         <v>181</v>
       </c>
@@ -3894,7 +3873,7 @@
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" ht="48" spans="1:9">
+    <row r="46" ht="48" hidden="1" spans="1:9">
       <c r="A46" s="9" t="s">
         <v>183</v>
       </c>
@@ -3917,7 +3896,7 @@
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" ht="48" spans="1:9">
+    <row r="47" ht="48" hidden="1" spans="1:9">
       <c r="A47" s="9" t="s">
         <v>186</v>
       </c>
@@ -3940,7 +3919,7 @@
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" ht="48" spans="1:9">
+    <row r="48" ht="48" hidden="1" spans="1:9">
       <c r="A48" s="9" t="s">
         <v>189</v>
       </c>
@@ -3963,7 +3942,7 @@
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" ht="48" spans="1:9">
+    <row r="49" ht="48" hidden="1" spans="1:9">
       <c r="A49" s="9" t="s">
         <v>191</v>
       </c>
@@ -3986,7 +3965,7 @@
       </c>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" ht="48" spans="1:9">
+    <row r="50" ht="48" hidden="1" spans="1:9">
       <c r="A50" s="9" t="s">
         <v>194</v>
       </c>
@@ -4009,7 +3988,7 @@
       </c>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" ht="48" spans="1:9">
+    <row r="51" ht="48" hidden="1" spans="1:9">
       <c r="A51" s="9" t="s">
         <v>197</v>
       </c>
@@ -4032,7 +4011,7 @@
       </c>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" ht="48" spans="1:9">
+    <row r="52" ht="48" hidden="1" spans="1:9">
       <c r="A52" s="9" t="s">
         <v>200</v>
       </c>
@@ -4055,7 +4034,7 @@
       </c>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" ht="48" spans="1:9">
+    <row r="53" ht="48" hidden="1" spans="1:9">
       <c r="A53" s="9" t="s">
         <v>203</v>
       </c>
@@ -4078,7 +4057,7 @@
       </c>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" hidden="1" spans="1:9">
       <c r="A54" s="9" t="s">
         <v>206</v>
       </c>
@@ -4101,7 +4080,7 @@
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" ht="24" spans="1:9">
+    <row r="55" ht="24" hidden="1" spans="1:9">
       <c r="A55" s="9" t="s">
         <v>209</v>
       </c>
@@ -4122,24 +4101,24 @@
       <c r="H55" s="9"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="39" t="s">
+    <row r="56" hidden="1" spans="1:9">
+      <c r="A56" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-    </row>
-    <row r="57" ht="72" spans="1:7">
+      <c r="B56" s="37"/>
+      <c r="C56" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+    </row>
+    <row r="57" ht="72" hidden="1" spans="1:7">
       <c r="A57" s="4" t="s">
         <v>213</v>
       </c>
@@ -4160,16 +4139,16 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" hidden="1" spans="1:9">
       <c r="A58" s="28" t="s">
         <v>216</v>
       </c>
       <c r="B58" s="29"/>
-      <c r="C58" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
+      <c r="C58" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
       <c r="F58" s="29" t="s">
         <v>65</v>
       </c>
@@ -4189,19 +4168,19 @@
       </c>
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
-      <c r="F59" s="41" t="s">
+      <c r="F59" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="38" t="s">
+      <c r="G59" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="H59" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J59" s="43" t="s">
+      <c r="J59" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K59" s="44"/>
+      <c r="K59" s="39"/>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4" t="s">
@@ -4221,16 +4200,16 @@
       <c r="G60" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J60" s="43" t="s">
+      <c r="J60" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K60" s="44"/>
-    </row>
-    <row r="61" ht="24" spans="1:9">
-      <c r="A61" s="33" t="s">
+      <c r="K60" s="39"/>
+    </row>
+    <row r="61" ht="24" hidden="1" spans="1:9">
+      <c r="A61" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="33" t="s">
         <v>225</v>
       </c>
       <c r="C61" s="10" t="s">
@@ -4238,17 +4217,17 @@
       </c>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
-      <c r="F61" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G61" s="33" t="s">
+      <c r="F61" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G61" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="H61" s="33"/>
-      <c r="I61" s="33"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="38" t="s">
+      <c r="A62" s="4" t="s">
         <v>227</v>
       </c>
       <c r="B62" s="21" t="s">
@@ -4259,22 +4238,22 @@
       </c>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
-      <c r="F62" s="41" t="s">
+      <c r="F62" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J62" s="43" t="s">
+      <c r="J62" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K62" s="44"/>
-    </row>
-    <row r="63" ht="24" spans="1:9">
-      <c r="A63" s="33" t="s">
+      <c r="K62" s="39"/>
+    </row>
+    <row r="63" ht="24" hidden="1" spans="1:9">
+      <c r="A63" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="33" t="s">
         <v>231</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -4282,16 +4261,16 @@
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="10"/>
-      <c r="F63" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G63" s="33" t="s">
+      <c r="F63" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-    </row>
-    <row r="64" ht="24" spans="1:7">
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+    </row>
+    <row r="64" ht="24" hidden="1" spans="1:7">
       <c r="A64" s="4" t="s">
         <v>232</v>
       </c>
@@ -4310,7 +4289,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65" s="4" t="s">
         <v>235</v>
       </c>
@@ -4331,16 +4310,16 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" hidden="1" spans="1:9">
       <c r="A66" s="28" t="s">
         <v>239</v>
       </c>
       <c r="B66" s="29"/>
-      <c r="C66" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40" t="s">
+      <c r="C66" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37" t="s">
         <v>237</v>
       </c>
       <c r="F66" s="29" t="s">
@@ -4350,7 +4329,7 @@
       <c r="H66" s="28"/>
       <c r="I66" s="28"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67" s="4" t="s">
         <v>240</v>
       </c>
@@ -4372,10 +4351,10 @@
       </c>
     </row>
     <row r="68" ht="96" spans="1:11">
-      <c r="A68" s="33" t="s">
+      <c r="A68" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="B68" s="34"/>
+      <c r="B68" s="33"/>
       <c r="C68" s="10" t="s">
         <v>124</v>
       </c>
@@ -4383,37 +4362,35 @@
         <v>245</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="45" t="s">
+      <c r="F68" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="46" t="s">
+      <c r="G68" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="H68" s="33" t="s">
+      <c r="H68" s="32" t="s">
         <v>247</v>
       </c>
       <c r="I68" s="28"/>
-      <c r="J68" s="43" t="s">
+      <c r="J68" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K68" s="44" t="s">
+      <c r="K68" s="39"/>
+    </row>
+    <row r="69" hidden="1" spans="1:9">
+      <c r="A69" s="28" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="28" t="s">
+      <c r="B69" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="B69" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D69" s="40" t="s">
+      <c r="C69" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="E69" s="40"/>
+      <c r="E69" s="37"/>
       <c r="F69" s="29" t="s">
         <v>65</v>
       </c>
@@ -4421,16 +4398,16 @@
       <c r="H69" s="28"/>
       <c r="I69" s="28"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" hidden="1" spans="1:9">
       <c r="A70" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B70" s="29"/>
-      <c r="C70" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
+      <c r="C70" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
       <c r="F70" s="29" t="s">
         <v>65</v>
       </c>
@@ -4438,16 +4415,16 @@
       <c r="H70" s="28"/>
       <c r="I70" s="28"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" hidden="1" spans="1:9">
       <c r="A71" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B71" s="29"/>
-      <c r="C71" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
+      <c r="C71" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
       <c r="F71" s="29" t="s">
         <v>65</v>
       </c>
@@ -4455,16 +4432,16 @@
       <c r="H71" s="28"/>
       <c r="I71" s="28"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" hidden="1" spans="1:9">
       <c r="A72" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B72" s="29"/>
-      <c r="C72" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
+      <c r="C72" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
       <c r="F72" s="29" t="s">
         <v>65</v>
       </c>
@@ -4472,16 +4449,16 @@
       <c r="H72" s="28"/>
       <c r="I72" s="28"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" hidden="1" spans="1:9">
       <c r="A73" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B73" s="29"/>
-      <c r="C73" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
+      <c r="C73" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
       <c r="F73" s="29" t="s">
         <v>65</v>
       </c>
@@ -4489,16 +4466,16 @@
       <c r="H73" s="28"/>
       <c r="I73" s="28"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" hidden="1" spans="1:9">
       <c r="A74" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="29"/>
-      <c r="C74" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
+      <c r="C74" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
       <c r="F74" s="29" t="s">
         <v>65</v>
       </c>
@@ -4506,33 +4483,33 @@
       <c r="H74" s="28"/>
       <c r="I74" s="28"/>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="33" t="s">
+    <row r="75" hidden="1" spans="1:9">
+      <c r="A75" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B75" s="33" t="s">
         <v>256</v>
-      </c>
-      <c r="B75" s="34" t="s">
-        <v>257</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
-      <c r="F75" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G75" s="33" t="s">
+      <c r="F75" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G75" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+    </row>
+    <row r="76" ht="60" hidden="1" spans="1:7">
+      <c r="A76" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
-    </row>
-    <row r="76" ht="60" spans="1:7">
-      <c r="A76" s="4" t="s">
+      <c r="B76" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>260</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>124</v>
@@ -4543,61 +4520,61 @@
         <v>65</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B77" s="21" t="s">
         <v>262</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>263</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
-      <c r="F77" s="41" t="s">
+      <c r="F77" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="J77" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="J77" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K77" s="44"/>
+      <c r="K77" s="39"/>
     </row>
     <row r="78" ht="60" spans="1:11">
       <c r="A78" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B78" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>266</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
-      <c r="F78" s="41" t="s">
+      <c r="F78" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G78" s="38" t="s">
+      <c r="G78" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="J78" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="K78" s="39"/>
+    </row>
+    <row r="79" ht="24" hidden="1" spans="1:7">
+      <c r="A79" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="J78" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="K78" s="44"/>
-    </row>
-    <row r="79" ht="24" spans="1:7">
-      <c r="A79" s="4" t="s">
+      <c r="B79" s="21" t="s">
         <v>268</v>
-      </c>
-      <c r="B79" s="21" t="s">
-        <v>269</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>124</v>
@@ -4608,15 +4585,15 @@
         <v>65</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="80" ht="24" hidden="1" spans="1:7">
+      <c r="A80" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="80" ht="24" spans="1:7">
-      <c r="A80" s="4" t="s">
+      <c r="B80" s="21" t="s">
         <v>271</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>272</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>124</v>
@@ -4630,12 +4607,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B81" s="21" t="s">
         <v>273</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>274</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>124</v>
@@ -4651,33 +4628,33 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B82" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>276</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
-      <c r="F82" s="41" t="s">
+      <c r="F82" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="J82" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="J82" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K82" s="44"/>
+      <c r="K82" s="39"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B83" s="21" t="s">
         <v>278</v>
-      </c>
-      <c r="B83" s="21" t="s">
-        <v>279</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>124</v>
@@ -4690,16 +4667,16 @@
       <c r="G83" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J83" s="43" t="s">
+      <c r="J83" s="39" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B84" s="21" t="s">
         <v>280</v>
-      </c>
-      <c r="B84" s="21" t="s">
-        <v>281</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>124</v>
@@ -4710,19 +4687,19 @@
         <v>65</v>
       </c>
       <c r="G84" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="85" hidden="1" spans="1:9">
+      <c r="A85" s="28" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="28" t="s">
-        <v>283</v>
-      </c>
       <c r="B85" s="29"/>
-      <c r="C85" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
+      <c r="C85" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
       <c r="F85" s="29" t="s">
         <v>65</v>
       </c>
@@ -4732,37 +4709,37 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B86" s="21" t="s">
         <v>284</v>
-      </c>
-      <c r="B86" s="21" t="s">
-        <v>285</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
-      <c r="F86" s="41" t="s">
+      <c r="F86" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J86" s="43" t="s">
+      <c r="J86" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K86" s="44"/>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="K86" s="39"/>
+    </row>
+    <row r="87" hidden="1" spans="1:9">
       <c r="A87" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B87" s="29"/>
-      <c r="C87" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
+      <c r="C87" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" s="37"/>
+      <c r="E87" s="37"/>
       <c r="F87" s="29" t="s">
         <v>65</v>
       </c>
@@ -4770,16 +4747,16 @@
       <c r="H87" s="28"/>
       <c r="I87" s="28"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" hidden="1" spans="1:9">
       <c r="A88" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B88" s="29"/>
-      <c r="C88" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
+      <c r="C88" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88" s="37"/>
+      <c r="E88" s="37"/>
       <c r="F88" s="29" t="s">
         <v>65</v>
       </c>
@@ -4787,16 +4764,16 @@
       <c r="H88" s="28"/>
       <c r="I88" s="28"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" hidden="1" spans="1:9">
       <c r="A89" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" s="29"/>
-      <c r="C89" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D89" s="40"/>
-      <c r="E89" s="40"/>
+      <c r="C89" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D89" s="37"/>
+      <c r="E89" s="37"/>
       <c r="F89" s="29" t="s">
         <v>65</v>
       </c>
@@ -4804,16 +4781,16 @@
       <c r="H89" s="28"/>
       <c r="I89" s="28"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" hidden="1" spans="1:9">
       <c r="A90" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B90" s="29"/>
-      <c r="C90" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" s="40"/>
-      <c r="E90" s="40"/>
+      <c r="C90" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="37"/>
+      <c r="E90" s="37"/>
       <c r="F90" s="29" t="s">
         <v>65</v>
       </c>
@@ -4821,16 +4798,16 @@
       <c r="H90" s="28"/>
       <c r="I90" s="28"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" hidden="1" spans="1:9">
       <c r="A91" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B91" s="29"/>
-      <c r="C91" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D91" s="40"/>
-      <c r="E91" s="40"/>
+      <c r="C91" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
       <c r="F91" s="29" t="s">
         <v>65</v>
       </c>
@@ -4838,16 +4815,16 @@
       <c r="H91" s="28"/>
       <c r="I91" s="28"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" hidden="1" spans="1:9">
       <c r="A92" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B92" s="29"/>
-      <c r="C92" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D92" s="40"/>
-      <c r="E92" s="40"/>
+      <c r="C92" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92" s="37"/>
+      <c r="E92" s="37"/>
       <c r="F92" s="29" t="s">
         <v>65</v>
       </c>
@@ -4855,16 +4832,16 @@
       <c r="H92" s="28"/>
       <c r="I92" s="28"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" hidden="1" spans="1:9">
       <c r="A93" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B93" s="29"/>
-      <c r="C93" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D93" s="40"/>
-      <c r="E93" s="40"/>
+      <c r="C93" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
       <c r="F93" s="29" t="s">
         <v>65</v>
       </c>
@@ -4872,16 +4849,16 @@
       <c r="H93" s="28"/>
       <c r="I93" s="28"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" hidden="1" spans="1:9">
       <c r="A94" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B94" s="29"/>
-      <c r="C94" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D94" s="40"/>
-      <c r="E94" s="40"/>
+      <c r="C94" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D94" s="37"/>
+      <c r="E94" s="37"/>
       <c r="F94" s="29" t="s">
         <v>65</v>
       </c>
@@ -4889,13 +4866,13 @@
       <c r="H94" s="28"/>
       <c r="I94" s="28"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" hidden="1" spans="1:9">
       <c r="A95" s="28" t="s">
         <v>212</v>
       </c>
       <c r="B95" s="29"/>
       <c r="C95" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D95" s="29"/>
       <c r="E95" s="29"/>
@@ -4906,13 +4883,13 @@
       <c r="H95" s="28"/>
       <c r="I95" s="28"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" hidden="1" spans="1:9">
       <c r="A96" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B96" s="29"/>
       <c r="C96" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D96" s="29"/>
       <c r="E96" s="29"/>
@@ -4923,13 +4900,13 @@
       <c r="H96" s="28"/>
       <c r="I96" s="28"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" hidden="1" spans="1:9">
       <c r="A97" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B97" s="29"/>
       <c r="C97" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D97" s="29"/>
       <c r="E97" s="29"/>
@@ -4940,15 +4917,15 @@
       <c r="H97" s="28"/>
       <c r="I97" s="28"/>
     </row>
-    <row r="98" ht="72" spans="1:10">
+    <row r="98" ht="72" hidden="1" spans="1:10">
       <c r="A98" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B98" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="C98" s="21" t="s">
         <v>298</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>299</v>
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
@@ -4956,42 +4933,42 @@
         <v>65</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="J98" s="43"/>
+        <v>299</v>
+      </c>
+      <c r="J98" s="39"/>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B99" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="B99" s="21" t="s">
-        <v>302</v>
-      </c>
       <c r="C99" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
-      <c r="F99" s="41" t="s">
+      <c r="F99" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J99" s="43" t="s">
+      <c r="J99" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K99" s="44"/>
-    </row>
-    <row r="100" ht="72" spans="1:7">
+      <c r="K99" s="39"/>
+    </row>
+    <row r="100" ht="72" hidden="1" spans="1:7">
       <c r="A100" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B100" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="B100" s="21" t="s">
-        <v>304</v>
-      </c>
       <c r="C100" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -4999,18 +4976,18 @@
         <v>65</v>
       </c>
       <c r="G100" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="1:9">
+      <c r="A101" s="28" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="28" t="s">
+      <c r="B101" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="B101" s="29" t="s">
-        <v>307</v>
-      </c>
       <c r="C101" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D101" s="29"/>
       <c r="E101" s="29"/>
@@ -5019,19 +4996,19 @@
       </c>
       <c r="G101" s="28"/>
       <c r="H101" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="I101" s="28"/>
+    </row>
+    <row r="102" hidden="1" spans="1:9">
+      <c r="A102" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="I101" s="28"/>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="28" t="s">
+      <c r="B102" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="B102" s="29" t="s">
-        <v>310</v>
-      </c>
       <c r="C102" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D102" s="29"/>
       <c r="E102" s="29"/>
@@ -5042,15 +5019,15 @@
       <c r="H102" s="28"/>
       <c r="I102" s="28"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" hidden="1" spans="1:9">
       <c r="A103" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="B103" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="B103" s="29" t="s">
-        <v>312</v>
-      </c>
       <c r="C103" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D103" s="29"/>
       <c r="E103" s="29"/>
@@ -5061,15 +5038,15 @@
       <c r="H103" s="28"/>
       <c r="I103" s="28"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" hidden="1" spans="1:9">
       <c r="A104" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="B104" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="B104" s="29" t="s">
-        <v>314</v>
-      </c>
       <c r="C104" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D104" s="29"/>
       <c r="E104" s="29"/>
@@ -5080,15 +5057,15 @@
       <c r="H104" s="28"/>
       <c r="I104" s="28"/>
     </row>
-    <row r="105" ht="24" spans="1:7">
+    <row r="105" ht="24" hidden="1" spans="1:7">
       <c r="A105" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B105" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="B105" s="21" t="s">
-        <v>316</v>
-      </c>
       <c r="C105" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
@@ -5096,18 +5073,18 @@
         <v>65</v>
       </c>
       <c r="G105" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="106" ht="60" spans="1:10">
+      <c r="A106" s="4" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="106" ht="60" spans="1:10">
-      <c r="A106" s="38" t="s">
+      <c r="B106" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="B106" s="21" t="s">
-        <v>319</v>
-      </c>
       <c r="C106" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
@@ -5115,44 +5092,44 @@
         <v>65</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="J106" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="J106" s="39" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="107" ht="24" spans="1:11">
       <c r="A107" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B107" s="21" t="s">
         <v>321</v>
-      </c>
-      <c r="B107" s="21" t="s">
-        <v>322</v>
       </c>
       <c r="C107" s="21" t="s">
         <v>161</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
-      <c r="F107" s="41" t="s">
+      <c r="F107" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G107" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="J107" s="43" t="s">
+      <c r="G107" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J107" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K107" s="44"/>
+      <c r="K107" s="39"/>
     </row>
     <row r="108" ht="72" spans="1:10">
       <c r="A108" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B108" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="B108" s="21" t="s">
-        <v>325</v>
-      </c>
       <c r="C108" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
@@ -5160,53 +5137,61 @@
         <v>65</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J108" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="J108" s="39" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="109" ht="24" spans="1:11">
       <c r="A109" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B109" s="21" t="s">
         <v>327</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>328</v>
       </c>
       <c r="C109" s="21"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
-      <c r="F109" s="41" t="s">
+      <c r="F109" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="J109" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="J109" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K109" s="44"/>
+      <c r="K109" s="39"/>
     </row>
     <row r="110" ht="36" spans="1:11">
       <c r="A110" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="F110" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F110" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J110" s="43" t="s">
+      <c r="J110" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="K110" s="44"/>
-    </row>
+      <c r="K110" s="39"/>
+    </row>
+    <row r="111" hidden="1"/>
+    <row r="112" hidden="1"/>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J112">
+    <filterColumn colId="9">
+      <customFilters>
+        <customFilter operator="equal" val="y"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:G102">
     <sortCondition ref="C2:C102"/>
   </sortState>

--- a/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
+++ b/internal_doc/03.开发设计/OM/om_sequoiadb_operation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26670" windowHeight="11910" activeTab="1"/>
+    <workbookView windowWidth="28695" windowHeight="13050" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 增加flag，数字和字符串两种格式
 后续版本新增的命令，参数名采用括号内名字。逐渐替换掉旧的名字</t>
         </r>
@@ -44,11 +43,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 可以暂时不支持多条</t>
         </r>
       </text>
@@ -58,11 +56,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 sort-》orderby
 增加flag，下同
 兼容处理</t>
@@ -74,11 +71,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 增加flag</t>
         </r>
       </text>
@@ -88,7 +84,6 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
@@ -103,11 +98,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 需要直连数据节点！</t>
         </r>
       </text>
@@ -117,11 +111,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 归到 list collectionspaces domain做为参数</t>
         </r>
       </text>
@@ -131,11 +124,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Author:
+          <t>Author:
 isasync -》 flag</t>
         </r>
       </text>
@@ -1215,7 +1207,7 @@
 options：设置其他属性</t>
   </si>
   <si>
-    <t>cmd=create domain&amp;options={"AutoSplit":true,{"Groups":["g1","g2"]}}</t>
+    <t>cmd=create domain&amp;options={"AutoSplit":true,"Groups":["g1","g2"]}</t>
   </si>
   <si>
     <t>create group</t>
@@ -1589,11 +1581,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1615,8 +1607,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1629,9 +1622,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1639,15 +1631,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1662,17 +1646,53 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1683,8 +1703,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1699,68 +1744,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1848,13 +1833,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1872,25 +1857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1908,7 +1875,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1926,7 +1929,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1938,31 +1959,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1974,19 +1995,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1998,31 +2007,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2077,17 +2062,61 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2096,7 +2125,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2116,61 +2145,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2182,10 +2167,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2194,138 +2179,138 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -2408,9 +2393,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2467,6 +2449,7 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
@@ -2768,7 +2751,7 @@
       </c>
     </row>
     <row r="2" ht="27" spans="1:1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4365,7 +4348,7 @@
       <c r="F68" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="40" t="s">
+      <c r="G68" s="32" t="s">
         <v>246</v>
       </c>
       <c r="H68" s="32" t="s">
